--- a/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023</t>
+          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,47 +780,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>7175</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2914</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7122</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1625</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1625</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,82 +1182,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1625</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3712</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32766</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,82 +1536,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7294</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12187</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>19633</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>11777</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>38286</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7294</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12049</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>19633</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>11844</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>38386</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28470</t>
+          <t>29481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>54449</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41382</t>
+          <t>40384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66776</t>
+          <t>66052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48133</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76831</t>
+          <t>76329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108926</t>
+          <t>108526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>232892</t>
+          <t>235366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>269498</t>
+          <t>270541</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>253566</t>
+          <t>253552</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>278575</t>
+          <t>278775</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>496580</t>
+          <t>498261</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>542650</t>
+          <t>542235</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2429,97 +2429,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1499</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2655,97 +2655,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>1066</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>6123</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>6461</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>5379</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34391</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21691</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>51455</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>26636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>59596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20622</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50288</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87356</t>
+          <t>91303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>45461</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>73498</t>
+          <t>75050</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44406</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66660</t>
+          <t>67736</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>94851</t>
+          <t>94926</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>132182</t>
+          <t>132506</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>332903</t>
+          <t>334768</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>383006</t>
+          <t>381817</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>345562</t>
+          <t>347428</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>380009</t>
+          <t>380861</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>693925</t>
+          <t>694287</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>754947</t>
+          <t>751803</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17206</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3902,97 +3902,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>849</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>164</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4128,97 +4128,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5488</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>1393</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>5957</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>5344</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>353</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>158064</t>
+          <t>164774</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>178704</t>
+          <t>164022</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>50950</t>
+          <t>49559</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>73589</t>
+          <t>75632</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>27383</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>52018</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>68549</t>
+          <t>68167</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>216138</t>
+          <t>217811</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>256183</t>
+          <t>256998</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>323184</t>
+          <t>325552</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>501476</t>
+          <t>505040</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>570169</t>
+          <t>570626</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>777200</t>
+          <t>767502</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5375,97 +5375,97 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>2687</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -5601,97 +5601,97 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>3760</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>3480</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,77 +5729,77 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>8865</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>15981</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>3219</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>7301</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>8865</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>4792</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>15990</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>23560</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>36599</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>49544</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>77587</t>
+          <t>78079</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>46601</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>69925</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>103666</t>
+          <t>101903</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>139896</t>
+          <t>137924</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>341456</t>
+          <t>339828</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>381750</t>
+          <t>382750</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>414703</t>
+          <t>413905</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>446075</t>
+          <t>445317</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>768351</t>
+          <t>769682</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>817178</t>
+          <t>818697</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,48%</t>
         </is>
       </c>
     </row>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34500</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>56925</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6848,82 +6848,82 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3025</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7011,47 +7011,47 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>6958</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2988</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>14177</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>6958</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>2989</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>15528</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,74 +7089,74 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>8808</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>9455</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>9435</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>1382</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>9165</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
           <t>0,04%</t>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>49676</t>
+          <t>50470</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>65897</t>
+          <t>66248</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>218708</t>
+          <t>193213</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>80025</t>
+          <t>79237</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>239294</t>
+          <t>258990</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>73581</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>78520</t>
+          <t>77744</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>134861</t>
+          <t>131878</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>57592</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>99422</t>
+          <t>99232</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>146865</t>
+          <t>142242</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>217481</t>
+          <t>220409</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -7752,12 +7752,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>165292</t>
+          <t>166850</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>218082</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>122740</t>
+          <t>122472</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>210604</t>
+          <t>209894</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>300038</t>
+          <t>300886</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>410084</t>
+          <t>410475</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>1173195</t>
+          <t>1172583</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1257849</t>
+          <t>1257039</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>1404113</t>
+          <t>1405072</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1610666</t>
+          <t>1605310</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>2613514</t>
+          <t>2615583</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>2857112</t>
+          <t>2854479</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>885</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1516,32 +1516,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29481</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23706</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>34205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41551</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31749</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54449</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>52491</t>
+          <t>54031</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40384</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66052</t>
+          <t>69466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>32044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>50833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91261</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76329</t>
+          <t>78420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108526</t>
+          <t>111274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1968,32 +1968,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>254144</t>
+          <t>277179</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>235366</t>
+          <t>256872</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>270541</t>
+          <t>293487</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2003,32 +2003,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>266850</t>
+          <t>287717</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>253552</t>
+          <t>274428</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>278775</t>
+          <t>300521</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2038,32 +2038,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>520994</t>
+          <t>564896</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>498261</t>
+          <t>542603</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>542235</t>
+          <t>586853</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -2081,17 +2081,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>377410</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>377410</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>377410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>381392</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>381392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>381392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>702742</t>
+          <t>758802</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702742</t>
+          <t>758802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>702742</t>
+          <t>758802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>746</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,22 +2381,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,22 +2833,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>862</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>36246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,67 +3024,67 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>35704</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>58902</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>33080</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>21691</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>51455</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59596</t>
+          <t>55419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>40610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>66816</t>
+          <t>68148</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52835</t>
+          <t>52789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>91303</t>
+          <t>88465</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -3328,32 +3328,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57605</t>
+          <t>62949</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45461</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>75050</t>
+          <t>79163</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3363,32 +3363,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>58328</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44406</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67736</t>
+          <t>71355</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3398,32 +3398,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>111969</t>
+          <t>121277</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>94926</t>
+          <t>103748</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>132506</t>
+          <t>141936</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -3441,32 +3441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>360288</t>
+          <t>390125</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>334768</t>
+          <t>362324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>381817</t>
+          <t>410683</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3476,32 +3476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>365335</t>
+          <t>408681</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>347428</t>
+          <t>389719</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>380861</t>
+          <t>427296</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3511,32 +3511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>725624</t>
+          <t>798807</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>694287</t>
+          <t>763117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>751803</t>
+          <t>825276</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>500419</t>
+          <t>536982</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>500419</t>
+          <t>536982</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>500419</t>
+          <t>536982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>530296</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>530296</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>530296</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>979350</t>
+          <t>1067278</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>979350</t>
+          <t>1067278</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>979350</t>
+          <t>1067278</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,32 +3671,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>19003</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3784,32 +3784,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21335</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3819,32 +3819,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>12779</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>29648</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>48673</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>164774</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>164022</t>
+          <t>38601</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4575,32 +4575,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>23506</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>36841</t>
+          <t>36561</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4688,32 +4688,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>35295</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>49559</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4723,32 +4723,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>23444</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>34904</t>
+          <t>34572</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4758,32 +4758,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>49029</t>
+          <t>58739</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>42525</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>75632</t>
+          <t>79254</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>22298</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>52018</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>55254</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>72151</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>239318</t>
+          <t>266447</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>217811</t>
+          <t>244056</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>256998</t>
+          <t>285591</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,32 +4949,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>421997</t>
+          <t>257725</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>325552</t>
+          <t>239816</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>505040</t>
+          <t>272591</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,32 +4984,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>661315</t>
+          <t>524172</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>570626</t>
+          <t>499663</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>767502</t>
+          <t>553244</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -5027,17 +5027,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>331443</t>
+          <t>374250</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>331443</t>
+          <t>374250</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>331443</t>
+          <t>374250</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,17 +5062,17 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>544536</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>544536</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>544536</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>875979</t>
+          <t>739123</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>875979</t>
+          <t>739123</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>875979</t>
+          <t>739123</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5179,22 +5179,22 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -5257,102 +5257,102 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>14446</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>17528</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>10319</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>27303</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>7102</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>16465</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>9584</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>455</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>459</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>746</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>746</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,22 +5892,22 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18761</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6048,32 +6048,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6083,32 +6083,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6118,32 +6118,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6161,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6196,32 +6196,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>44631</t>
+          <t>36537</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -6274,32 +6274,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>48447</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>78079</t>
+          <t>79337</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6309,17 +6309,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>57355</t>
+          <t>62817</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>46601</t>
+          <t>51145</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>70514</t>
+          <t>75065</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6344,32 +6344,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>119395</t>
+          <t>126761</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>101903</t>
+          <t>108730</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>137924</t>
+          <t>146339</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -6387,32 +6387,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>364196</t>
+          <t>397479</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>339828</t>
+          <t>377452</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>382750</t>
+          <t>416929</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6422,32 +6422,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>430820</t>
+          <t>472040</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>413905</t>
+          <t>454565</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>445317</t>
+          <t>486458</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6457,32 +6457,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>795017</t>
+          <t>869520</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>769682</t>
+          <t>843453</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>818697</t>
+          <t>892613</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6500,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>475202</t>
+          <t>512433</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>475202</t>
+          <t>512433</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>475202</t>
+          <t>512433</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>529558</t>
+          <t>579920</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>529558</t>
+          <t>579920</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>529558</t>
+          <t>579920</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1004761</t>
+          <t>1092353</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1004761</t>
+          <t>1092353</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1004761</t>
+          <t>1092353</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,102 +6617,102 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>12294</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>23261</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>25600</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>17012</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>39584</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>5623</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>21812</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>22967</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>14626</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>34500</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -6730,32 +6730,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>42946</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>63188</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6956,32 +6956,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6991,32 +6991,32 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -7104,27 +7104,27 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>29655</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>53727</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -7295,97 +7295,97 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>7718</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>19903</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>15606</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>34242</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>12249</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>7078</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>19382</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>22709</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="inlineStr">
-        <is>
-          <t>14534</t>
-        </is>
-      </c>
-      <c r="T62" s="2" t="inlineStr">
-        <is>
-          <t>33329</t>
-        </is>
-      </c>
-      <c r="U62" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>66248</t>
+          <t>69958</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>67758</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7478,32 +7478,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>120940</t>
+          <t>98302</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>79237</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>258990</t>
+          <t>127040</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7521,32 +7521,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>52351</t>
+          <t>55974</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7591,32 +7591,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>59629</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>77475</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -7634,32 +7634,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>100839</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>77744</t>
+          <t>82904</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>134298</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7669,32 +7669,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>92052</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>57592</t>
+          <t>78101</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>110705</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7704,32 +7704,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>181318</t>
+          <t>198544</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>142242</t>
+          <t>171018</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>220409</t>
+          <t>229259</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7747,32 +7747,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>190204</t>
+          <t>204442</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>166850</t>
+          <t>177455</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>218082</t>
+          <t>229810</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>178265</t>
+          <t>193335</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>122472</t>
+          <t>171171</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>209894</t>
+          <t>217738</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>368470</t>
+          <t>397778</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>300886</t>
+          <t>364134</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>410475</t>
+          <t>436288</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -7860,32 +7860,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1217946</t>
+          <t>1331230</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>1172583</t>
+          <t>1284265</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1257039</t>
+          <t>1369981</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>1485002</t>
+          <t>1426164</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>1405072</t>
+          <t>1391742</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1605310</t>
+          <t>1458383</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>2702949</t>
+          <t>2757393</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>2615583</t>
+          <t>2704879</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>2854479</t>
+          <t>2809037</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -7973,17 +7973,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8043,17 +8043,17 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">

--- a/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
